--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.01719</v>
+        <v>16.88133</v>
       </c>
       <c r="D2" t="n">
-        <v>16.65162</v>
+        <v>16.72329</v>
       </c>
       <c r="E2" t="n">
-        <v>16.60963</v>
+        <v>16.7658</v>
       </c>
       <c r="F2" t="n">
-        <v>43.40635</v>
+        <v>42.09223</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04998</v>
+        <v>0.05027</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84903</v>
+        <v>1.82856</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.81307</v>
+        <v>16.79467</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75503</v>
+        <v>16.61696</v>
       </c>
       <c r="E3" t="n">
-        <v>16.50605</v>
+        <v>16.65456</v>
       </c>
       <c r="F3" t="n">
-        <v>40.38683</v>
+        <v>42.98491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05079</v>
+        <v>0.05264</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8483</v>
+        <v>1.81451</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.70725</v>
+        <v>16.93317</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61871</v>
+        <v>16.58559</v>
       </c>
       <c r="E4" t="n">
-        <v>16.83002</v>
+        <v>16.83495</v>
       </c>
       <c r="F4" t="n">
-        <v>43.34254</v>
+        <v>42.86113</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05148</v>
+        <v>0.05037</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8486</v>
+        <v>1.86306</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.05405</v>
+        <v>16.66788</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18497</v>
+        <v>16.26019</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33717</v>
+        <v>16.58612</v>
       </c>
       <c r="F6" t="n">
-        <v>21.91224</v>
+        <v>21.74495</v>
       </c>
       <c r="G6" t="n">
-        <v>34.159</v>
+        <v>33.81918</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88466</v>
+        <v>16.92035</v>
       </c>
       <c r="D7" t="n">
-        <v>15.81578</v>
+        <v>15.59246</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32883</v>
+        <v>16.09742</v>
       </c>
       <c r="F7" t="n">
-        <v>22.18301</v>
+        <v>21.42787</v>
       </c>
       <c r="G7" t="n">
-        <v>34.73687</v>
+        <v>34.82102</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83741</v>
+        <v>16.71468</v>
       </c>
       <c r="D8" t="n">
-        <v>16.47528</v>
+        <v>15.84798</v>
       </c>
       <c r="E8" t="n">
-        <v>16.61156</v>
+        <v>16.58391</v>
       </c>
       <c r="F8" t="n">
-        <v>21.8713</v>
+        <v>21.83033</v>
       </c>
       <c r="G8" t="n">
-        <v>33.64891</v>
+        <v>33.90101</v>
       </c>
     </row>
   </sheetData>
